--- a/hira_material_automation/output/monthly/202601_202607__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04T22:02:58</t>
+          <t>2026-07-14T22:02:48</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a22ebe56ee27c942ce5ef679f70d261bdc7fb6e808cc24d30b3f4577cb57c89f</t>
+          <t>596e04f95ea19384b5f8a15e0c08b85854c80345536cf1fdd5ebb74e50960c98</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202607__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T22:02:48</t>
+          <t>2026-07-24T22:09:43</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>596e04f95ea19384b5f8a15e0c08b85854c80345536cf1fdd5ebb74e50960c98</t>
+          <t>d5432713f01b9800752710982181968f15af076c6171cbb1cfcf3f744ba444b1</t>
         </is>
       </c>
     </row>
